--- a/artfynd/A 30989-2024 artfynd.xlsx
+++ b/artfynd/A 30989-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675729</v>
+        <v>118675730</v>
       </c>
       <c r="B2" t="n">
-        <v>97869</v>
+        <v>79566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497198</v>
+        <v>497212</v>
       </c>
       <c r="R2" t="n">
-        <v>6959097</v>
+        <v>6959101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675731</v>
+        <v>118675729</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>97869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497205</v>
+        <v>497198</v>
       </c>
       <c r="R3" t="n">
-        <v>6959098</v>
+        <v>6959097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675730</v>
+        <v>118675731</v>
       </c>
       <c r="B4" t="n">
-        <v>79566</v>
+        <v>79565</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497212</v>
+        <v>497205</v>
       </c>
       <c r="R4" t="n">
-        <v>6959101</v>
+        <v>6959098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 30989-2024 artfynd.xlsx
+++ b/artfynd/A 30989-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118675730</v>
       </c>
       <c r="B2" t="n">
-        <v>79566</v>
+        <v>79573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>118675729</v>
       </c>
       <c r="B3" t="n">
-        <v>97869</v>
+        <v>97876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>118675731</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30989-2024 artfynd.xlsx
+++ b/artfynd/A 30989-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675730</v>
+        <v>118675731</v>
       </c>
       <c r="B2" t="n">
-        <v>79573</v>
+        <v>79572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497212</v>
+        <v>497205</v>
       </c>
       <c r="R2" t="n">
-        <v>6959101</v>
+        <v>6959098</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675731</v>
+        <v>118675730</v>
       </c>
       <c r="B4" t="n">
-        <v>79572</v>
+        <v>79573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497205</v>
+        <v>497212</v>
       </c>
       <c r="R4" t="n">
-        <v>6959098</v>
+        <v>6959101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 30989-2024 artfynd.xlsx
+++ b/artfynd/A 30989-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675731</v>
+        <v>118675730</v>
       </c>
       <c r="B2" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497205</v>
+        <v>497212</v>
       </c>
       <c r="R2" t="n">
-        <v>6959098</v>
+        <v>6959101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675729</v>
+        <v>118675731</v>
       </c>
       <c r="B3" t="n">
-        <v>97881</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497198</v>
+        <v>497205</v>
       </c>
       <c r="R3" t="n">
-        <v>6959097</v>
+        <v>6959098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675730</v>
+        <v>118675729</v>
       </c>
       <c r="B4" t="n">
-        <v>79575</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497212</v>
+        <v>497198</v>
       </c>
       <c r="R4" t="n">
-        <v>6959101</v>
+        <v>6959097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 30989-2024 artfynd.xlsx
+++ b/artfynd/A 30989-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675730</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675731</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675729</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>